--- a/assets/docs/Dimitri-Tableau de synthese.xlsx
+++ b/assets/docs/Dimitri-Tableau de synthese.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\portfolio\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B9814F-7464-4513-9F54-67DED9FCCCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41974B48-2EF3-465D-BEB0-6CC7C99D994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -118,9 +118,6 @@
   <si>
     <t xml:space="preserve">Réalisation en cours de formation
 </t>
-  </si>
-  <si>
-    <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
     <r>
@@ -193,6 +190,18 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>19/01/2026 au 27/02/2026</t>
+  </si>
+  <si>
+    <t>Développement : Participer à la création de formulaires de maintenance dans le cadre d’un ERP Développement : Participer à la création de workflows opérationnels dans le cadre d’un ERP Développement : Participer à la modification et à l’ajout de nouvelles fonctionnalités aux applications existantes
+Tests / QA : Tester et s’assurer que les modules ou modifications développés répondent aux exigences et aux résultats attendus
+Tests / QA : Tester les modifications réalisées par les coéquipiers afin de s’assurer que les exigences sont respectées
+Solution IA : Créer et entraîner un modèle d’intelligence artificielle basé sur les besoins du client et les objectifs du projet</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel en cours de seconde année : FRCI</t>
   </si>
 </sst>
 </file>
@@ -774,15 +783,39 @@
     <xf numFmtId="16" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -823,30 +856,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1169,56 +1178,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="52"/>
+      <c r="A3" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="36"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50"/>
+      <c r="A4" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,26 +1235,26 @@
         <v>4</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
+      <c r="A5" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="52"/>
     </row>
     <row r="6" spans="1:43" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="48" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1268,8 +1277,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="221.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="19" t="s">
         <v>13</v>
       </c>
@@ -1325,16 +1334,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="21"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1373,24 +1382,24 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="203" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1430,24 +1439,24 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="223" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1487,14 +1496,14 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="281" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
@@ -1537,16 +1546,16 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="36"/>
+      <c r="A12" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1585,22 +1594,24 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="228.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="22"/>
+        <v>23</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
       <c r="F13" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1639,16 +1650,16 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
+      <c r="A14" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1685,15 +1696,25 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="352" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>34</v>
+      </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="E15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="22" t="s">
+        <v>33</v>
+      </c>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -2093,11 +2114,6 @@
     <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2105,6 +2121,11 @@
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2115,21 +2136,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010021F7977E49F44542ABC169D3385720BE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2cf713f46d33035be00877ff8f959ac0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3e941104-c427-4bbd-984f-032c9c413468" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4c16e54e4b70d5728734523a24a24c88" ns2:_="">
     <xsd:import namespace="3e941104-c427-4bbd-984f-032c9c413468"/>
@@ -2267,31 +2273,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E2624D4-D0F5-4CDD-8F7C-B158102636B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3e941104-c427-4bbd-984f-032c9c413468"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76564368-5BF8-48E2-AA91-E85E538DFFE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD92159-81FB-4C72-AE74-77C4F4A0B31E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2307,4 +2304,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76564368-5BF8-48E2-AA91-E85E538DFFE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E2624D4-D0F5-4CDD-8F7C-B158102636B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3e941104-c427-4bbd-984f-032c9c413468"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/docs/Dimitri-Tableau de synthese.xlsx
+++ b/assets/docs/Dimitri-Tableau de synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\portfolio\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41974B48-2EF3-465D-BEB0-6CC7C99D994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613E17B6-08F1-4CCB-BEF1-8069600FFA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -165,43 +165,40 @@
     <t>01/10/2024  au 01/03/2025</t>
   </si>
   <si>
-    <t>N° candidat : 2542605401</t>
-  </si>
-  <si>
-    <t>06/10/2025 au 26/11/2025</t>
-  </si>
-  <si>
-    <t>VMS est une application dédiée à la gestion des bons d’achat. Elle permet aux utilisateurs de créer, suivre et valider des bons d’achat de manière efficace, tout en offrant aux administrateurs des fonctionnalités avancées pour gérer les utilisateurs, contrôler l’historique des transactions et générer des rapports détaillés. L’application assure ainsi une organisation optimale et sécurisée du processus de bons d’achat au sein de l’entreprise.</t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de première année : Acensi Mauritius</t>
   </si>
   <si>
-    <t>Un site web de concession automobile nommé Supercar composé de deux parties distinctes : une interface cliente permettant aux utilisateurs de consulter les véhicules, vérifier leurs caractéristiques et effectuer des demandes, et une partie administrative offrant aux gestionnaires les outils nécessaires pour ajouter, modifier ou supprimer des véhicules, gérer les utilisateurs ainsi que suivre les réservations et les activités du site.</t>
-  </si>
-  <si>
-    <t>Mise en place d’une solution de gestion du support informatique et des équipements avec GLPI. Ce projet permet de centraliser et d’optimiser le suivi des incidents et des demandes des utilisateurs, tout en offrant un inventaire complet et structuré du parc informatique. Les administrateurs peuvent gérer les tickets, les équipements, les contrats et les licences, tandis que les utilisateurs bénéficient d’une interface claire pour signaler des problèmes et suivre l’avancement de leurs demandes. L’ensemble améliore l’efficacité du service informatique et la traçabilité des interventions.</t>
-  </si>
-  <si>
-    <t>Conception et développement d’un CRM pour centraliser la gestion des clients. L’application permet de suivre les interactions, les ventes et les opportunités. Elle offre aux équipes un outil efficace pour améliorer la relation client et optimiser les processus commerciaux.</t>
-  </si>
-  <si>
-    <t>X SLAM</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
     <t>19/01/2026 au 27/02/2026</t>
   </si>
   <si>
-    <t>Développement : Participer à la création de formulaires de maintenance dans le cadre d’un ERP Développement : Participer à la création de workflows opérationnels dans le cadre d’un ERP Développement : Participer à la modification et à l’ajout de nouvelles fonctionnalités aux applications existantes
-Tests / QA : Tester et s’assurer que les modules ou modifications développés répondent aux exigences et aux résultats attendus
-Tests / QA : Tester les modifications réalisées par les coéquipiers afin de s’assurer que les exigences sont respectées
-Solution IA : Créer et entraîner un modèle d’intelligence artificielle basé sur les besoins du client et les objectifs du projet</t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de seconde année : FRCI</t>
+  </si>
+  <si>
+    <t>▢ SLAM</t>
+  </si>
+  <si>
+    <t>Supercar : site web de gestion et de consultation de véhicules avec espace client et administration</t>
+  </si>
+  <si>
+    <t>VMS : application de gestion des bons d’achat avec espace utilisateur et administration</t>
+  </si>
+  <si>
+    <t>Développement et tests d’applications ERP avec intégration de solutions d’intelligence artificielle</t>
+  </si>
+  <si>
+    <t>CRM : conception et développement d’une application de gestion centralisée des clients</t>
+  </si>
+  <si>
+    <t>06/10/2025 au 3/04/2026</t>
+  </si>
+  <si>
+    <t>Gestion Patrimoine : GLPI et Agent Fusion Inventory / GLPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° candidat : 02542605401 </t>
   </si>
 </sst>
 </file>
@@ -309,7 +306,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -414,51 +411,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
     <border diagonalDown="1">
       <left style="medium">
         <color theme="2" tint="-0.749992370372631"/>
@@ -696,6 +648,36 @@
       <diagonal style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </diagonal>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -728,15 +710,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -746,32 +719,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -783,79 +750,94 @@
     <xf numFmtId="16" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -874,6 +856,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>535360</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>168183</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>729286</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>362109</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Graphique 4" descr="Fermer avec un remplissage uni">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848784F5-7065-B8F6-635B-A6F0B153E446}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17982741" y="1710326"/>
+          <a:ext cx="193926" cy="193926"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1178,83 +1215,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="36"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="46"/>
+      <c r="H3" s="52"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="12" t="s">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>32</v>
+      <c r="H4" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="52"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:43" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="40" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1276,25 +1313,25 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="221.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="19" t="s">
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="239.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I7"/>
@@ -1334,17 +1371,17 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="21"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="16"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8"/>
@@ -1380,26 +1417,28 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="203" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="26" t="s">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="262.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>33</v>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1437,26 +1476,26 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="223" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="25" t="s">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="200" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>33</v>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1494,21 +1533,21 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="281" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>30</v>
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="191.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="B11" s="8"/>
-      <c r="C11" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
+      <c r="C11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1546,16 +1585,16 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
+      <c r="A12" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1592,26 +1631,26 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="228.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="27" t="s">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="231.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>33</v>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1650,16 +1689,16 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
+      <c r="A14" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1696,24 +1735,26 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="352" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="230.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>26</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -1752,14 +1793,14 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1797,14 +1838,14 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1842,14 +1883,14 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1887,14 +1928,14 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1932,14 +1973,14 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1976,15 +2017,15 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17"/>
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2114,6 +2155,11 @@
     <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2121,21 +2167,26 @@
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="37" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010021F7977E49F44542ABC169D3385720BE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2cf713f46d33035be00877ff8f959ac0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3e941104-c427-4bbd-984f-032c9c413468" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4c16e54e4b70d5728734523a24a24c88" ns2:_="">
     <xsd:import namespace="3e941104-c427-4bbd-984f-032c9c413468"/>
@@ -2273,15 +2324,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2289,6 +2331,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76564368-5BF8-48E2-AA91-E85E538DFFE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD92159-81FB-4C72-AE74-77C4F4A0B31E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2306,26 +2356,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76564368-5BF8-48E2-AA91-E85E538DFFE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E2624D4-D0F5-4CDD-8F7C-B158102636B5}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="3e941104-c427-4bbd-984f-032c9c413468"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>